--- a/Data/Fertilization.xlsx
+++ b/Data/Fertilization.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cgiar-my.sharepoint.com/personal/a_f_velez_cgiar_org/Documents/R_projects/Fertilice_right/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="159" documentId="8_{9FC7542B-8470-4AE6-AFDF-AA312FAC8D0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{98740BA4-8F8F-43AC-B295-B3536E3C18AE}"/>
+  <xr:revisionPtr revIDLastSave="170" documentId="8_{9FC7542B-8470-4AE6-AFDF-AA312FAC8D0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1A4652F3-9011-497A-98C6-14599287DEA9}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{CD6BA171-ACC6-4A4B-BBE3-E98F686B030A}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{CD6BA171-ACC6-4A4B-BBE3-E98F686B030A}"/>
   </bookViews>
   <sheets>
     <sheet name="Colnames" sheetId="3" r:id="rId1"/>
@@ -28,7 +28,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Costos!$A$1:$D$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Fertilizations!$A$1:$L$245</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Rendimiento!$A$1:$K$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Soil_results C1'!$A$1:$AK$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Soil_results C1'!$A$1:$AK$37</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1184,12 +1184,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F14B0B36-3C8A-4797-80D6-7C6C0ED0768E}">
   <dimension ref="A1:B37"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
         <v>129</v>
       </c>
@@ -1197,22 +1197,22 @@
         <v>130</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>81</v>
       </c>
@@ -1220,7 +1220,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>82</v>
       </c>
@@ -1228,7 +1228,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>83</v>
       </c>
@@ -1236,12 +1236,12 @@
         <v>132</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>85</v>
       </c>
@@ -1249,7 +1249,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>86</v>
       </c>
@@ -1257,7 +1257,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>87</v>
       </c>
@@ -1265,7 +1265,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>88</v>
       </c>
@@ -1273,12 +1273,12 @@
         <v>134</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>90</v>
       </c>
@@ -1286,7 +1286,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>91</v>
       </c>
@@ -1294,7 +1294,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>92</v>
       </c>
@@ -1302,7 +1302,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>93</v>
       </c>
@@ -1310,7 +1310,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>94</v>
       </c>
@@ -1318,7 +1318,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>95</v>
       </c>
@@ -1326,7 +1326,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>96</v>
       </c>
@@ -1334,7 +1334,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>97</v>
       </c>
@@ -1342,7 +1342,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>98</v>
       </c>
@@ -1350,7 +1350,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>99</v>
       </c>
@@ -1358,7 +1358,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>100</v>
       </c>
@@ -1366,7 +1366,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>101</v>
       </c>
@@ -1374,7 +1374,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>102</v>
       </c>
@@ -1382,7 +1382,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>103</v>
       </c>
@@ -1390,7 +1390,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>104</v>
       </c>
@@ -1398,7 +1398,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>105</v>
       </c>
@@ -1406,7 +1406,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>106</v>
       </c>
@@ -1414,7 +1414,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>107</v>
       </c>
@@ -1422,7 +1422,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>108</v>
       </c>
@@ -1430,7 +1430,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>109</v>
       </c>
@@ -1438,7 +1438,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>110</v>
       </c>
@@ -1446,7 +1446,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>142</v>
       </c>
@@ -1454,7 +1454,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>144</v>
       </c>
@@ -1462,7 +1462,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>146</v>
       </c>
@@ -1477,23 +1477,24 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2177DD21-2128-495B-96CE-BE1663CCD5C8}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:AK46"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.54296875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="12.7109375" customWidth="1"/>
-    <col min="8" max="8" width="21.28515625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="15.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="15.42578125" style="3" customWidth="1"/>
-    <col min="24" max="37" width="9.140625" customWidth="1"/>
+    <col min="6" max="6" width="12.7265625" customWidth="1"/>
+    <col min="8" max="8" width="21.26953125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="15.453125" style="3" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="15.453125" style="3" customWidth="1"/>
+    <col min="24" max="37" width="9.1796875" customWidth="1"/>
     <col min="38" max="39" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>77</v>
       </c>
@@ -1606,7 +1607,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>114</v>
       </c>
@@ -1721,7 +1722,7 @@
         <v>52.54</v>
       </c>
     </row>
-    <row r="3" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>118</v>
       </c>
@@ -1836,7 +1837,7 @@
         <v>41.86</v>
       </c>
     </row>
-    <row r="4" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>119</v>
       </c>
@@ -1951,7 +1952,7 @@
         <v>37.74</v>
       </c>
     </row>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>114</v>
       </c>
@@ -2066,7 +2067,7 @@
         <v>24.84</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>118</v>
       </c>
@@ -2181,7 +2182,7 @@
         <v>5.19</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>119</v>
       </c>
@@ -2296,7 +2297,7 @@
         <v>31.54</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>114</v>
       </c>
@@ -2411,7 +2412,7 @@
         <v>14.75</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>118</v>
       </c>
@@ -2526,7 +2527,7 @@
         <v>12.35</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>119</v>
       </c>
@@ -2641,7 +2642,7 @@
         <v>6.24</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:37" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>114</v>
       </c>
@@ -2756,7 +2757,7 @@
         <v>29.7</v>
       </c>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:37" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>118</v>
       </c>
@@ -2871,7 +2872,7 @@
         <v>21.44</v>
       </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:37" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>119</v>
       </c>
@@ -2986,7 +2987,7 @@
         <v>55.75</v>
       </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:37" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>114</v>
       </c>
@@ -3101,7 +3102,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:37" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>118</v>
       </c>
@@ -3212,7 +3213,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:37" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>119</v>
       </c>
@@ -3327,7 +3328,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:37" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>114</v>
       </c>
@@ -3442,7 +3443,7 @@
         <v>29.11</v>
       </c>
     </row>
-    <row r="18" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:37" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>118</v>
       </c>
@@ -3557,7 +3558,7 @@
         <v>99.16</v>
       </c>
     </row>
-    <row r="19" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:37" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>119</v>
       </c>
@@ -3672,7 +3673,7 @@
         <v>22.96</v>
       </c>
     </row>
-    <row r="20" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:37" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>114</v>
       </c>
@@ -3787,7 +3788,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:37" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>118</v>
       </c>
@@ -3902,7 +3903,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:37" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>119</v>
       </c>
@@ -4017,7 +4018,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:37" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>114</v>
       </c>
@@ -4132,7 +4133,7 @@
         <v>115.62</v>
       </c>
     </row>
-    <row r="24" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:37" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
         <v>118</v>
       </c>
@@ -4247,7 +4248,7 @@
         <v>58.84</v>
       </c>
     </row>
-    <row r="25" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:37" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>119</v>
       </c>
@@ -4362,7 +4363,7 @@
         <v>73.239999999999995</v>
       </c>
     </row>
-    <row r="26" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:37" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>114</v>
       </c>
@@ -4477,7 +4478,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="27" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:37" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>118</v>
       </c>
@@ -4592,7 +4593,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="28" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:37" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
         <v>119</v>
       </c>
@@ -4707,35 +4708,50 @@
         <v>21</v>
       </c>
     </row>
-    <row r="38" spans="24:24" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:37" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="30" spans="1:37" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="31" spans="1:37" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="32" spans="1:37" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="33" spans="24:24" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="34" spans="24:24" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="35" spans="24:24" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="36" spans="24:24" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="37" spans="24:24" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="38" spans="24:24" x14ac:dyDescent="0.35">
       <c r="X38" s="7"/>
     </row>
-    <row r="39" spans="24:24" x14ac:dyDescent="0.25">
+    <row r="39" spans="24:24" x14ac:dyDescent="0.35">
       <c r="X39" s="7"/>
     </row>
-    <row r="40" spans="24:24" x14ac:dyDescent="0.25">
+    <row r="40" spans="24:24" x14ac:dyDescent="0.35">
       <c r="X40" s="7"/>
     </row>
-    <row r="41" spans="24:24" x14ac:dyDescent="0.25">
+    <row r="41" spans="24:24" x14ac:dyDescent="0.35">
       <c r="X41" s="7"/>
     </row>
-    <row r="42" spans="24:24" x14ac:dyDescent="0.25">
+    <row r="42" spans="24:24" x14ac:dyDescent="0.35">
       <c r="X42" s="7"/>
     </row>
-    <row r="43" spans="24:24" x14ac:dyDescent="0.25">
+    <row r="43" spans="24:24" x14ac:dyDescent="0.35">
       <c r="X43" s="7"/>
     </row>
-    <row r="44" spans="24:24" x14ac:dyDescent="0.25">
+    <row r="44" spans="24:24" x14ac:dyDescent="0.35">
       <c r="X44" s="7"/>
     </row>
-    <row r="45" spans="24:24" x14ac:dyDescent="0.25">
+    <row r="45" spans="24:24" x14ac:dyDescent="0.35">
       <c r="X45" s="7"/>
     </row>
-    <row r="46" spans="24:24" x14ac:dyDescent="0.25">
+    <row r="46" spans="24:24" x14ac:dyDescent="0.35">
       <c r="X46" s="7"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AK37" xr:uid="{3594B106-9936-4E82-9D96-90BC8F73080E}"/>
+  <autoFilter ref="A1:AK37" xr:uid="{3594B106-9936-4E82-9D96-90BC8F73080E}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="Rice"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4743,14 +4759,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F66789E3-4B93-484F-A2E3-0BA1A61378CE}">
   <dimension ref="A1:AK10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="4" max="4" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.28515625" customWidth="1"/>
+    <col min="4" max="4" width="14.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.26953125" customWidth="1"/>
     <col min="16" max="16" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>77</v>
       </c>
@@ -4863,7 +4879,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>114</v>
       </c>
@@ -4980,7 +4996,7 @@
         <v>2.2400000000000002</v>
       </c>
     </row>
-    <row r="3" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>118</v>
       </c>
@@ -5097,7 +5113,7 @@
         <v>0.73</v>
       </c>
     </row>
-    <row r="4" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>119</v>
       </c>
@@ -5214,7 +5230,7 @@
         <v>3.04</v>
       </c>
     </row>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>114</v>
       </c>
@@ -5331,7 +5347,7 @@
         <v>1.18</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>118</v>
       </c>
@@ -5448,7 +5464,7 @@
         <v>0.96</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>119</v>
       </c>
@@ -5565,7 +5581,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>114</v>
       </c>
@@ -5682,7 +5698,7 @@
         <v>2.29</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>118</v>
       </c>
@@ -5799,7 +5815,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>119</v>
       </c>
@@ -5925,24 +5941,24 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E088276-5EC8-4C80-930B-550C3B35023C}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:O245"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="10.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.85546875" customWidth="1"/>
-    <col min="5" max="5" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.28515625" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.453125" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.81640625" customWidth="1"/>
+    <col min="5" max="5" width="15.26953125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.26953125" customWidth="1"/>
+    <col min="7" max="7" width="16.7265625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.7265625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.453125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.7265625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.54296875" bestFit="1" customWidth="1"/>
     <col min="14" max="15" width="16" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5989,7 +6005,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>15</v>
       </c>
@@ -6036,7 +6052,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>15</v>
       </c>
@@ -6083,7 +6099,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -6130,7 +6146,7 @@
         <v>9.99</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
@@ -6177,7 +6193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
@@ -6224,7 +6240,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>15</v>
       </c>
@@ -6271,7 +6287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>15</v>
       </c>
@@ -6318,7 +6334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>15</v>
       </c>
@@ -6365,7 +6381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>15</v>
       </c>
@@ -6412,7 +6428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>15</v>
       </c>
@@ -6459,7 +6475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>15</v>
       </c>
@@ -6508,7 +6524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>15</v>
       </c>
@@ -6555,7 +6571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>15</v>
       </c>
@@ -6602,7 +6618,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>15</v>
       </c>
@@ -6649,7 +6665,7 @@
         <v>24.96</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>15</v>
       </c>
@@ -6696,7 +6712,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>15</v>
       </c>
@@ -6744,7 +6760,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>15</v>
       </c>
@@ -6791,7 +6807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>15</v>
       </c>
@@ -6838,7 +6854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>15</v>
       </c>
@@ -6885,7 +6901,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>15</v>
       </c>
@@ -6934,7 +6950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>15</v>
       </c>
@@ -6981,7 +6997,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>15</v>
       </c>
@@ -7028,7 +7044,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
         <v>15</v>
       </c>
@@ -7075,7 +7091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>15</v>
       </c>
@@ -7122,7 +7138,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>15</v>
       </c>
@@ -7169,7 +7185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>15</v>
       </c>
@@ -7216,7 +7232,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
         <v>15</v>
       </c>
@@ -7263,7 +7279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
         <v>15</v>
       </c>
@@ -7310,7 +7326,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
         <v>15</v>
       </c>
@@ -7357,7 +7373,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
         <v>15</v>
       </c>
@@ -7404,7 +7420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
         <v>15</v>
       </c>
@@ -7451,7 +7467,7 @@
         <v>24.96</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
         <v>15</v>
       </c>
@@ -7498,7 +7514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
         <v>15</v>
       </c>
@@ -7545,7 +7561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
         <v>15</v>
       </c>
@@ -7592,7 +7608,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
         <v>15</v>
       </c>
@@ -7639,7 +7655,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
         <v>15</v>
       </c>
@@ -7686,7 +7702,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
         <v>38</v>
       </c>
@@ -7734,7 +7750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
         <v>38</v>
       </c>
@@ -7782,7 +7798,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
         <v>38</v>
       </c>
@@ -7830,7 +7846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
         <v>38</v>
       </c>
@@ -7878,7 +7894,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
         <v>38</v>
       </c>
@@ -7926,7 +7942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
         <v>38</v>
       </c>
@@ -7974,7 +7990,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
         <v>38</v>
       </c>
@@ -8022,7 +8038,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
         <v>38</v>
       </c>
@@ -8070,7 +8086,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
         <v>38</v>
       </c>
@@ -8118,7 +8134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
         <v>38</v>
       </c>
@@ -8168,7 +8184,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
         <v>38</v>
       </c>
@@ -8216,7 +8232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49" s="1" t="s">
         <v>38</v>
       </c>
@@ -8264,7 +8280,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
         <v>38</v>
       </c>
@@ -8312,7 +8328,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
         <v>38</v>
       </c>
@@ -8360,7 +8376,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
         <v>38</v>
       </c>
@@ -8408,7 +8424,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
         <v>38</v>
       </c>
@@ -8456,7 +8472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
         <v>38</v>
       </c>
@@ -8504,7 +8520,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="s">
         <v>38</v>
       </c>
@@ -8552,7 +8568,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56" s="1" t="s">
         <v>38</v>
       </c>
@@ -8600,7 +8616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57" s="1" t="s">
         <v>38</v>
       </c>
@@ -8648,7 +8664,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A58" s="1" t="s">
         <v>38</v>
       </c>
@@ -8696,7 +8712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A59" s="1" t="s">
         <v>38</v>
       </c>
@@ -8746,7 +8762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A60" s="1" t="s">
         <v>38</v>
       </c>
@@ -8794,7 +8810,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A61" s="1" t="s">
         <v>38</v>
       </c>
@@ -8842,7 +8858,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A62" s="1" t="s">
         <v>38</v>
       </c>
@@ -8890,7 +8906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A63" s="1" t="s">
         <v>38</v>
       </c>
@@ -8938,7 +8954,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A64" s="1" t="s">
         <v>38</v>
       </c>
@@ -8986,7 +9002,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A65" s="1" t="s">
         <v>38</v>
       </c>
@@ -9034,7 +9050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A66" s="1" t="s">
         <v>38</v>
       </c>
@@ -9082,7 +9098,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A67" s="1" t="s">
         <v>38</v>
       </c>
@@ -9132,7 +9148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A68" s="1" t="s">
         <v>38</v>
       </c>
@@ -9180,7 +9196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A69" s="1" t="s">
         <v>38</v>
       </c>
@@ -9228,7 +9244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A70" s="1" t="s">
         <v>38</v>
       </c>
@@ -9276,7 +9292,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A71" s="1" t="s">
         <v>38</v>
       </c>
@@ -9324,7 +9340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A72" s="1" t="s">
         <v>38</v>
       </c>
@@ -9372,7 +9388,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A73" s="1" t="s">
         <v>38</v>
       </c>
@@ -9420,7 +9436,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A74" s="1" t="s">
         <v>40</v>
       </c>
@@ -9468,7 +9484,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A75" s="1" t="s">
         <v>40</v>
       </c>
@@ -9516,7 +9532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A76" s="1" t="s">
         <v>40</v>
       </c>
@@ -9564,7 +9580,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A77" s="1" t="s">
         <v>40</v>
       </c>
@@ -9612,7 +9628,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A78" s="1" t="s">
         <v>40</v>
       </c>
@@ -9660,7 +9676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A79" s="1" t="s">
         <v>40</v>
       </c>
@@ -9708,7 +9724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A80" s="1" t="s">
         <v>40</v>
       </c>
@@ -9756,7 +9772,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A81" s="1" t="s">
         <v>40</v>
       </c>
@@ -9804,7 +9820,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A82" s="1" t="s">
         <v>40</v>
       </c>
@@ -9852,7 +9868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A83" s="1" t="s">
         <v>40</v>
       </c>
@@ -9900,7 +9916,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A84" s="1" t="s">
         <v>40</v>
       </c>
@@ -9950,7 +9966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A85" s="1" t="s">
         <v>40</v>
       </c>
@@ -9998,7 +10014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A86" s="1" t="s">
         <v>40</v>
       </c>
@@ -10046,7 +10062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A87" s="1" t="s">
         <v>40</v>
       </c>
@@ -10094,7 +10110,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A88" s="1" t="s">
         <v>40</v>
       </c>
@@ -10142,7 +10158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A89" s="1" t="s">
         <v>40</v>
       </c>
@@ -10190,7 +10206,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A90" s="1" t="s">
         <v>40</v>
       </c>
@@ -10238,7 +10254,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A91" s="1" t="s">
         <v>40</v>
       </c>
@@ -10286,7 +10302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A92" s="1" t="s">
         <v>40</v>
       </c>
@@ -10334,7 +10350,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A93" s="1" t="s">
         <v>40</v>
       </c>
@@ -10382,7 +10398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A94" s="1" t="s">
         <v>40</v>
       </c>
@@ -10430,7 +10446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A95" s="1" t="s">
         <v>40</v>
       </c>
@@ -10478,7 +10494,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A96" s="1" t="s">
         <v>40</v>
       </c>
@@ -10528,7 +10544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A97" s="1" t="s">
         <v>40</v>
       </c>
@@ -10576,7 +10592,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A98" s="1" t="s">
         <v>40</v>
       </c>
@@ -10624,7 +10640,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A99" s="1" t="s">
         <v>40</v>
       </c>
@@ -10672,7 +10688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A100" s="1" t="s">
         <v>40</v>
       </c>
@@ -10720,7 +10736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A101" s="1" t="s">
         <v>40</v>
       </c>
@@ -10768,7 +10784,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A102" s="1" t="s">
         <v>40</v>
       </c>
@@ -10816,7 +10832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A103" s="1" t="s">
         <v>40</v>
       </c>
@@ -10864,7 +10880,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A104" s="1" t="s">
         <v>40</v>
       </c>
@@ -10912,7 +10928,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A105" s="1" t="s">
         <v>40</v>
       </c>
@@ -10960,7 +10976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A106" s="1" t="s">
         <v>40</v>
       </c>
@@ -11008,7 +11024,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A107" s="1" t="s">
         <v>40</v>
       </c>
@@ -11056,7 +11072,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A108" s="1" t="s">
         <v>40</v>
       </c>
@@ -11104,7 +11120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A109" s="1" t="s">
         <v>40</v>
       </c>
@@ -11152,7 +11168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A110" s="1" t="s">
         <v>40</v>
       </c>
@@ -11200,7 +11216,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A111" s="1" t="s">
         <v>40</v>
       </c>
@@ -11248,7 +11264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A112" s="1" t="s">
         <v>40</v>
       </c>
@@ -11296,7 +11312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A113" s="1" t="s">
         <v>40</v>
       </c>
@@ -11344,7 +11360,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="114" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A114" s="1" t="s">
         <v>15</v>
       </c>
@@ -11396,7 +11412,7 @@
         <v>36.72</v>
       </c>
     </row>
-    <row r="115" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A115" s="1" t="s">
         <v>15</v>
       </c>
@@ -11444,7 +11460,7 @@
         <v>55.08</v>
       </c>
     </row>
-    <row r="116" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A116" s="1" t="s">
         <v>15</v>
       </c>
@@ -11492,7 +11508,7 @@
         <v>55.08</v>
       </c>
     </row>
-    <row r="117" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A117" s="1" t="s">
         <v>15</v>
       </c>
@@ -11542,7 +11558,7 @@
         <v>36.72</v>
       </c>
     </row>
-    <row r="118" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A118" s="1" t="s">
         <v>15</v>
       </c>
@@ -11594,7 +11610,7 @@
         <v>39.1</v>
       </c>
     </row>
-    <row r="119" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A119" s="1" t="s">
         <v>15</v>
       </c>
@@ -11646,7 +11662,7 @@
         <v>36.72</v>
       </c>
     </row>
-    <row r="120" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A120" s="1" t="s">
         <v>15</v>
       </c>
@@ -11699,7 +11715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A121" s="1" t="s">
         <v>15</v>
       </c>
@@ -11751,7 +11767,7 @@
         <v>24.48</v>
       </c>
     </row>
-    <row r="122" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A122" s="1" t="s">
         <v>15</v>
       </c>
@@ -11803,7 +11819,7 @@
         <v>61.199999999999996</v>
       </c>
     </row>
-    <row r="123" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A123" s="1" t="s">
         <v>15</v>
       </c>
@@ -11855,7 +11871,7 @@
         <v>122.39999999999999</v>
       </c>
     </row>
-    <row r="124" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A124" s="1" t="s">
         <v>15</v>
       </c>
@@ -11907,7 +11923,7 @@
         <v>48.96</v>
       </c>
     </row>
-    <row r="125" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A125" s="1" t="s">
         <v>15</v>
       </c>
@@ -11959,7 +11975,7 @@
         <v>73.44</v>
       </c>
     </row>
-    <row r="126" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A126" s="1" t="s">
         <v>15</v>
       </c>
@@ -12011,7 +12027,7 @@
         <v>61.199999999999996</v>
       </c>
     </row>
-    <row r="127" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A127" s="1" t="s">
         <v>15</v>
       </c>
@@ -12063,7 +12079,7 @@
         <v>36.72</v>
       </c>
     </row>
-    <row r="128" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A128" s="1" t="s">
         <v>15</v>
       </c>
@@ -12115,7 +12131,7 @@
         <v>122.39999999999999</v>
       </c>
     </row>
-    <row r="129" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A129" s="1" t="s">
         <v>15</v>
       </c>
@@ -12167,7 +12183,7 @@
         <v>39.1</v>
       </c>
     </row>
-    <row r="130" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A130" s="1" t="s">
         <v>38</v>
       </c>
@@ -12219,7 +12235,7 @@
         <v>36.72</v>
       </c>
     </row>
-    <row r="131" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A131" s="1" t="s">
         <v>38</v>
       </c>
@@ -12267,7 +12283,7 @@
         <v>55.08</v>
       </c>
     </row>
-    <row r="132" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A132" s="1" t="s">
         <v>38</v>
       </c>
@@ -12315,7 +12331,7 @@
         <v>55.08</v>
       </c>
     </row>
-    <row r="133" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A133" s="1" t="s">
         <v>38</v>
       </c>
@@ -12365,7 +12381,7 @@
         <v>36.72</v>
       </c>
     </row>
-    <row r="134" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A134" s="1" t="s">
         <v>38</v>
       </c>
@@ -12417,7 +12433,7 @@
         <v>39.1</v>
       </c>
     </row>
-    <row r="135" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A135" s="1" t="s">
         <v>38</v>
       </c>
@@ -12469,7 +12485,7 @@
         <v>36.72</v>
       </c>
     </row>
-    <row r="136" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A136" s="1" t="s">
         <v>38</v>
       </c>
@@ -12522,7 +12538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A137" s="1" t="s">
         <v>38</v>
       </c>
@@ -12574,7 +12590,7 @@
         <v>24.48</v>
       </c>
     </row>
-    <row r="138" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A138" s="1" t="s">
         <v>38</v>
       </c>
@@ -12626,7 +12642,7 @@
         <v>61.199999999999996</v>
       </c>
     </row>
-    <row r="139" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A139" s="1" t="s">
         <v>38</v>
       </c>
@@ -12678,7 +12694,7 @@
         <v>122.39999999999999</v>
       </c>
     </row>
-    <row r="140" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A140" s="1" t="s">
         <v>38</v>
       </c>
@@ -12730,7 +12746,7 @@
         <v>48.96</v>
       </c>
     </row>
-    <row r="141" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A141" s="1" t="s">
         <v>38</v>
       </c>
@@ -12782,7 +12798,7 @@
         <v>73.44</v>
       </c>
     </row>
-    <row r="142" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A142" s="1" t="s">
         <v>38</v>
       </c>
@@ -12834,7 +12850,7 @@
         <v>61.199999999999996</v>
       </c>
     </row>
-    <row r="143" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A143" s="1" t="s">
         <v>38</v>
       </c>
@@ -12886,7 +12902,7 @@
         <v>36.72</v>
       </c>
     </row>
-    <row r="144" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A144" s="1" t="s">
         <v>38</v>
       </c>
@@ -12938,7 +12954,7 @@
         <v>122.39999999999999</v>
       </c>
     </row>
-    <row r="145" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A145" s="1" t="s">
         <v>38</v>
       </c>
@@ -12990,7 +13006,7 @@
         <v>39.1</v>
       </c>
     </row>
-    <row r="146" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A146" s="1" t="s">
         <v>40</v>
       </c>
@@ -13042,7 +13058,7 @@
         <v>36.72</v>
       </c>
     </row>
-    <row r="147" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A147" s="1" t="s">
         <v>40</v>
       </c>
@@ -13090,7 +13106,7 @@
         <v>55.08</v>
       </c>
     </row>
-    <row r="148" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A148" s="1" t="s">
         <v>40</v>
       </c>
@@ -13138,7 +13154,7 @@
         <v>55.08</v>
       </c>
     </row>
-    <row r="149" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A149" s="1" t="s">
         <v>40</v>
       </c>
@@ -13188,7 +13204,7 @@
         <v>36.72</v>
       </c>
     </row>
-    <row r="150" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A150" s="1" t="s">
         <v>40</v>
       </c>
@@ -13240,7 +13256,7 @@
         <v>39.1</v>
       </c>
     </row>
-    <row r="151" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A151" s="1" t="s">
         <v>40</v>
       </c>
@@ -13292,7 +13308,7 @@
         <v>36.72</v>
       </c>
     </row>
-    <row r="152" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A152" s="1" t="s">
         <v>40</v>
       </c>
@@ -13345,7 +13361,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A153" s="1" t="s">
         <v>40</v>
       </c>
@@ -13397,7 +13413,7 @@
         <v>24.48</v>
       </c>
     </row>
-    <row r="154" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A154" s="1" t="s">
         <v>40</v>
       </c>
@@ -13449,7 +13465,7 @@
         <v>61.199999999999996</v>
       </c>
     </row>
-    <row r="155" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A155" s="1" t="s">
         <v>40</v>
       </c>
@@ -13501,7 +13517,7 @@
         <v>122.39999999999999</v>
       </c>
     </row>
-    <row r="156" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A156" s="1" t="s">
         <v>40</v>
       </c>
@@ -13553,7 +13569,7 @@
         <v>48.96</v>
       </c>
     </row>
-    <row r="157" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A157" s="1" t="s">
         <v>40</v>
       </c>
@@ -13605,7 +13621,7 @@
         <v>73.44</v>
       </c>
     </row>
-    <row r="158" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A158" s="1" t="s">
         <v>40</v>
       </c>
@@ -13657,7 +13673,7 @@
         <v>61.199999999999996</v>
       </c>
     </row>
-    <row r="159" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A159" s="1" t="s">
         <v>40</v>
       </c>
@@ -13709,7 +13725,7 @@
         <v>36.72</v>
       </c>
     </row>
-    <row r="160" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A160" s="1" t="s">
         <v>40</v>
       </c>
@@ -13761,7 +13777,7 @@
         <v>122.39999999999999</v>
       </c>
     </row>
-    <row r="161" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A161" s="1" t="s">
         <v>40</v>
       </c>
@@ -13813,7 +13829,7 @@
         <v>39.1</v>
       </c>
     </row>
-    <row r="162" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A162" s="1" t="s">
         <v>15</v>
       </c>
@@ -13865,7 +13881,7 @@
         <v>46.92</v>
       </c>
     </row>
-    <row r="163" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A163" s="1" t="s">
         <v>15</v>
       </c>
@@ -13917,7 +13933,7 @@
         <v>55.080000000000005</v>
       </c>
     </row>
-    <row r="164" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A164" s="1" t="s">
         <v>15</v>
       </c>
@@ -13969,7 +13985,7 @@
         <v>45.900000000000006</v>
       </c>
     </row>
-    <row r="165" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A165" s="1" t="s">
         <v>15</v>
       </c>
@@ -14021,7 +14037,7 @@
         <v>55.080000000000005</v>
       </c>
     </row>
-    <row r="166" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A166" s="1" t="s">
         <v>15</v>
       </c>
@@ -14073,7 +14089,7 @@
         <v>39.1</v>
       </c>
     </row>
-    <row r="167" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A167" s="1" t="s">
         <v>15</v>
       </c>
@@ -14125,7 +14141,7 @@
         <v>40.799999999999997</v>
       </c>
     </row>
-    <row r="168" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A168" s="1" t="s">
         <v>15</v>
       </c>
@@ -14177,7 +14193,7 @@
         <v>40.799999999999997</v>
       </c>
     </row>
-    <row r="169" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A169" s="1" t="s">
         <v>15</v>
       </c>
@@ -14229,7 +14245,7 @@
         <v>40.799999999999997</v>
       </c>
     </row>
-    <row r="170" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A170" s="1" t="s">
         <v>15</v>
       </c>
@@ -14281,7 +14297,7 @@
         <v>61.199999999999996</v>
       </c>
     </row>
-    <row r="171" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A171" s="1" t="s">
         <v>15</v>
       </c>
@@ -14333,7 +14349,7 @@
         <v>61.199999999999996</v>
       </c>
     </row>
-    <row r="172" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A172" s="1" t="s">
         <v>15</v>
       </c>
@@ -14385,7 +14401,7 @@
         <v>61.199999999999996</v>
       </c>
     </row>
-    <row r="173" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A173" s="1" t="s">
         <v>15</v>
       </c>
@@ -14437,7 +14453,7 @@
         <v>61.199999999999996</v>
       </c>
     </row>
-    <row r="174" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A174" s="1" t="s">
         <v>15</v>
       </c>
@@ -14489,7 +14505,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A175" s="1" t="s">
         <v>15</v>
       </c>
@@ -14541,7 +14557,7 @@
         <v>39.1</v>
       </c>
     </row>
-    <row r="176" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A176" s="1" t="s">
         <v>38</v>
       </c>
@@ -14593,7 +14609,7 @@
         <v>54.74</v>
       </c>
     </row>
-    <row r="177" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A177" s="1" t="s">
         <v>38</v>
       </c>
@@ -14645,7 +14661,7 @@
         <v>64.260000000000005</v>
       </c>
     </row>
-    <row r="178" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A178" s="1" t="s">
         <v>38</v>
       </c>
@@ -14697,7 +14713,7 @@
         <v>55.080000000000005</v>
       </c>
     </row>
-    <row r="179" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A179" s="1" t="s">
         <v>38</v>
       </c>
@@ -14749,7 +14765,7 @@
         <v>64.260000000000005</v>
       </c>
     </row>
-    <row r="180" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A180" s="1" t="s">
         <v>38</v>
       </c>
@@ -14801,7 +14817,7 @@
         <v>39.1</v>
       </c>
     </row>
-    <row r="181" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A181" s="1" t="s">
         <v>38</v>
       </c>
@@ -14853,7 +14869,7 @@
         <v>40.799999999999997</v>
       </c>
     </row>
-    <row r="182" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A182" s="1" t="s">
         <v>38</v>
       </c>
@@ -14905,7 +14921,7 @@
         <v>40.799999999999997</v>
       </c>
     </row>
-    <row r="183" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A183" s="1" t="s">
         <v>38</v>
       </c>
@@ -14957,7 +14973,7 @@
         <v>40.799999999999997</v>
       </c>
     </row>
-    <row r="184" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A184" s="1" t="s">
         <v>38</v>
       </c>
@@ -15009,7 +15025,7 @@
         <v>61.199999999999996</v>
       </c>
     </row>
-    <row r="185" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A185" s="1" t="s">
         <v>38</v>
       </c>
@@ -15061,7 +15077,7 @@
         <v>61.199999999999996</v>
       </c>
     </row>
-    <row r="186" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A186" s="1" t="s">
         <v>38</v>
       </c>
@@ -15113,7 +15129,7 @@
         <v>61.199999999999996</v>
       </c>
     </row>
-    <row r="187" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A187" s="1" t="s">
         <v>38</v>
       </c>
@@ -15165,7 +15181,7 @@
         <v>61.199999999999996</v>
       </c>
     </row>
-    <row r="188" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A188" s="1" t="s">
         <v>38</v>
       </c>
@@ -15217,7 +15233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A189" s="1" t="s">
         <v>38</v>
       </c>
@@ -15269,7 +15285,7 @@
         <v>39.1</v>
       </c>
     </row>
-    <row r="190" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A190" s="1" t="s">
         <v>40</v>
       </c>
@@ -15321,7 +15337,7 @@
         <v>54.74</v>
       </c>
     </row>
-    <row r="191" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A191" s="1" t="s">
         <v>40</v>
       </c>
@@ -15373,7 +15389,7 @@
         <v>64.260000000000005</v>
       </c>
     </row>
-    <row r="192" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A192" s="1" t="s">
         <v>40</v>
       </c>
@@ -15425,7 +15441,7 @@
         <v>55.080000000000005</v>
       </c>
     </row>
-    <row r="193" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A193" s="1" t="s">
         <v>40</v>
       </c>
@@ -15477,7 +15493,7 @@
         <v>64.260000000000005</v>
       </c>
     </row>
-    <row r="194" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A194" s="1" t="s">
         <v>40</v>
       </c>
@@ -15529,7 +15545,7 @@
         <v>39.1</v>
       </c>
     </row>
-    <row r="195" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A195" s="1" t="s">
         <v>40</v>
       </c>
@@ -15581,7 +15597,7 @@
         <v>40.799999999999997</v>
       </c>
     </row>
-    <row r="196" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A196" s="1" t="s">
         <v>40</v>
       </c>
@@ -15633,7 +15649,7 @@
         <v>40.799999999999997</v>
       </c>
     </row>
-    <row r="197" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A197" s="1" t="s">
         <v>40</v>
       </c>
@@ -15685,7 +15701,7 @@
         <v>40.799999999999997</v>
       </c>
     </row>
-    <row r="198" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A198" s="1" t="s">
         <v>40</v>
       </c>
@@ -15737,7 +15753,7 @@
         <v>61.199999999999996</v>
       </c>
     </row>
-    <row r="199" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A199" s="1" t="s">
         <v>40</v>
       </c>
@@ -15789,7 +15805,7 @@
         <v>61.199999999999996</v>
       </c>
     </row>
-    <row r="200" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A200" s="1" t="s">
         <v>40</v>
       </c>
@@ -15841,7 +15857,7 @@
         <v>61.199999999999996</v>
       </c>
     </row>
-    <row r="201" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A201" s="1" t="s">
         <v>40</v>
       </c>
@@ -15893,7 +15909,7 @@
         <v>61.199999999999996</v>
       </c>
     </row>
-    <row r="202" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A202" s="1" t="s">
         <v>40</v>
       </c>
@@ -15945,7 +15961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A203" s="1" t="s">
         <v>40</v>
       </c>
@@ -15997,7 +16013,7 @@
         <v>39.1</v>
       </c>
     </row>
-    <row r="204" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A204" s="1" t="s">
         <v>15</v>
       </c>
@@ -16049,7 +16065,7 @@
         <v>54.74</v>
       </c>
     </row>
-    <row r="205" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A205" s="1" t="s">
         <v>15</v>
       </c>
@@ -16101,7 +16117,7 @@
         <v>64.260000000000005</v>
       </c>
     </row>
-    <row r="206" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A206" s="1" t="s">
         <v>15</v>
       </c>
@@ -16153,7 +16169,7 @@
         <v>55.080000000000005</v>
       </c>
     </row>
-    <row r="207" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A207" s="1" t="s">
         <v>15</v>
       </c>
@@ -16205,7 +16221,7 @@
         <v>64.260000000000005</v>
       </c>
     </row>
-    <row r="208" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A208" s="1" t="s">
         <v>15</v>
       </c>
@@ -16257,7 +16273,7 @@
         <v>39.1</v>
       </c>
     </row>
-    <row r="209" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A209" s="1" t="s">
         <v>15</v>
       </c>
@@ -16309,7 +16325,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="210" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A210" s="1" t="s">
         <v>15</v>
       </c>
@@ -16361,7 +16377,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="211" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A211" s="1" t="s">
         <v>15</v>
       </c>
@@ -16413,7 +16429,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="212" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A212" s="1" t="s">
         <v>15</v>
       </c>
@@ -16465,7 +16481,7 @@
         <v>71.399999999999991</v>
       </c>
     </row>
-    <row r="213" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A213" s="1" t="s">
         <v>15</v>
       </c>
@@ -16517,7 +16533,7 @@
         <v>71.399999999999991</v>
       </c>
     </row>
-    <row r="214" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A214" s="1" t="s">
         <v>15</v>
       </c>
@@ -16569,7 +16585,7 @@
         <v>71.399999999999991</v>
       </c>
     </row>
-    <row r="215" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A215" s="1" t="s">
         <v>15</v>
       </c>
@@ -16621,7 +16637,7 @@
         <v>71.399999999999991</v>
       </c>
     </row>
-    <row r="216" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A216" s="1" t="s">
         <v>15</v>
       </c>
@@ -16673,7 +16689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A217" s="1" t="s">
         <v>15</v>
       </c>
@@ -16725,7 +16741,7 @@
         <v>39.1</v>
       </c>
     </row>
-    <row r="218" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A218" s="1" t="s">
         <v>38</v>
       </c>
@@ -16777,7 +16793,7 @@
         <v>54.74</v>
       </c>
     </row>
-    <row r="219" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A219" s="1" t="s">
         <v>38</v>
       </c>
@@ -16829,7 +16845,7 @@
         <v>64.260000000000005</v>
       </c>
     </row>
-    <row r="220" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A220" s="1" t="s">
         <v>38</v>
       </c>
@@ -16881,7 +16897,7 @@
         <v>55.080000000000005</v>
       </c>
     </row>
-    <row r="221" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A221" s="1" t="s">
         <v>38</v>
       </c>
@@ -16933,7 +16949,7 @@
         <v>64.260000000000005</v>
       </c>
     </row>
-    <row r="222" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A222" s="1" t="s">
         <v>38</v>
       </c>
@@ -16985,7 +17001,7 @@
         <v>39.1</v>
       </c>
     </row>
-    <row r="223" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A223" s="1" t="s">
         <v>38</v>
       </c>
@@ -17037,7 +17053,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="224" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A224" s="1" t="s">
         <v>38</v>
       </c>
@@ -17089,7 +17105,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="225" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A225" s="1" t="s">
         <v>38</v>
       </c>
@@ -17141,7 +17157,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="226" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A226" s="1" t="s">
         <v>38</v>
       </c>
@@ -17193,7 +17209,7 @@
         <v>71.399999999999991</v>
       </c>
     </row>
-    <row r="227" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A227" s="1" t="s">
         <v>38</v>
       </c>
@@ -17245,7 +17261,7 @@
         <v>71.399999999999991</v>
       </c>
     </row>
-    <row r="228" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A228" s="1" t="s">
         <v>38</v>
       </c>
@@ -17297,7 +17313,7 @@
         <v>71.399999999999991</v>
       </c>
     </row>
-    <row r="229" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A229" s="1" t="s">
         <v>38</v>
       </c>
@@ -17349,7 +17365,7 @@
         <v>71.399999999999991</v>
       </c>
     </row>
-    <row r="230" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A230" s="1" t="s">
         <v>38</v>
       </c>
@@ -17401,7 +17417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A231" s="1" t="s">
         <v>38</v>
       </c>
@@ -17453,7 +17469,7 @@
         <v>39.1</v>
       </c>
     </row>
-    <row r="232" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A232" s="1" t="s">
         <v>40</v>
       </c>
@@ -17505,7 +17521,7 @@
         <v>54.74</v>
       </c>
     </row>
-    <row r="233" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A233" s="1" t="s">
         <v>40</v>
       </c>
@@ -17557,7 +17573,7 @@
         <v>64.260000000000005</v>
       </c>
     </row>
-    <row r="234" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A234" s="1" t="s">
         <v>40</v>
       </c>
@@ -17609,7 +17625,7 @@
         <v>55.080000000000005</v>
       </c>
     </row>
-    <row r="235" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A235" s="1" t="s">
         <v>40</v>
       </c>
@@ -17661,7 +17677,7 @@
         <v>64.260000000000005</v>
       </c>
     </row>
-    <row r="236" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A236" s="1" t="s">
         <v>40</v>
       </c>
@@ -17713,7 +17729,7 @@
         <v>39.1</v>
       </c>
     </row>
-    <row r="237" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A237" s="1" t="s">
         <v>40</v>
       </c>
@@ -17765,7 +17781,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="238" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A238" s="1" t="s">
         <v>40</v>
       </c>
@@ -17817,7 +17833,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="239" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A239" s="1" t="s">
         <v>40</v>
       </c>
@@ -17869,7 +17885,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="240" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A240" s="1" t="s">
         <v>40</v>
       </c>
@@ -17921,7 +17937,7 @@
         <v>71.399999999999991</v>
       </c>
     </row>
-    <row r="241" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A241" s="1" t="s">
         <v>40</v>
       </c>
@@ -17973,7 +17989,7 @@
         <v>71.399999999999991</v>
       </c>
     </row>
-    <row r="242" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A242" s="1" t="s">
         <v>40</v>
       </c>
@@ -18025,7 +18041,7 @@
         <v>71.399999999999991</v>
       </c>
     </row>
-    <row r="243" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A243" s="1" t="s">
         <v>40</v>
       </c>
@@ -18077,7 +18093,7 @@
         <v>71.399999999999991</v>
       </c>
     </row>
-    <row r="244" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A244" s="1" t="s">
         <v>40</v>
       </c>
@@ -18129,7 +18145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A245" s="1" t="s">
         <v>40</v>
       </c>
@@ -18185,7 +18201,7 @@
   <autoFilter ref="A1:L245" xr:uid="{3CA3D38B-9E40-4E9F-8415-A4349BC7491D}">
     <filterColumn colId="2">
       <filters>
-        <filter val="Arroz"/>
+        <filter val="Banano"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -18196,32 +18212,32 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC952D4E-0346-4EE6-9F3F-3B949C7BD82C}">
   <dimension ref="A1:W25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.453125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.5703125" customWidth="1"/>
-    <col min="7" max="7" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.7109375" customWidth="1"/>
-    <col min="11" max="11" width="22.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.54296875" customWidth="1"/>
+    <col min="7" max="7" width="21.54296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.81640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.7265625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.7265625" customWidth="1"/>
+    <col min="11" max="11" width="22.453125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7265625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.26953125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.81640625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="18" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="12.28515625" customWidth="1"/>
-    <col min="18" max="18" width="21.5703125" customWidth="1"/>
-    <col min="19" max="19" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.26953125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.26953125" customWidth="1"/>
+    <col min="18" max="18" width="21.54296875" customWidth="1"/>
+    <col min="19" max="19" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.26953125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -18292,7 +18308,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -18368,7 +18384,7 @@
         <v>1.5001344999999999</v>
       </c>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -18444,7 +18460,7 @@
         <v>1.35022</v>
       </c>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -18520,7 +18536,7 @@
         <v>1.5768800000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>38</v>
       </c>
@@ -18596,7 +18612,7 @@
         <v>1.1771042199999999</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>38</v>
       </c>
@@ -18672,7 +18688,7 @@
         <v>1.2602</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>38</v>
       </c>
@@ -18748,7 +18764,7 @@
         <v>1.8176399999999999</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>40</v>
       </c>
@@ -18824,7 +18840,7 @@
         <v>1.4087645999999998</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>40</v>
       </c>
@@ -18900,7 +18916,7 @@
         <v>1.55758</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>40</v>
       </c>
@@ -18976,25 +18992,25 @@
         <v>1.8697299999999999</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.35">
       <c r="H11" s="9"/>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.35">
       <c r="H12" s="9"/>
       <c r="S12" s="10"/>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.35">
       <c r="H13" s="9"/>
       <c r="I13" s="10"/>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
       <c r="D14" s="2"/>
       <c r="H14" s="9"/>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -19005,7 +19021,7 @@
       <c r="U15" s="10"/>
       <c r="V15" s="10"/>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -19017,7 +19033,7 @@
       <c r="V16" s="10"/>
       <c r="W16" s="10"/>
     </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -19029,7 +19045,7 @@
       <c r="V17" s="10"/>
       <c r="W17" s="10"/>
     </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -19041,7 +19057,7 @@
       <c r="V18" s="10"/>
       <c r="W18" s="10"/>
     </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -19054,7 +19070,7 @@
       <c r="V19" s="10"/>
       <c r="W19" s="10"/>
     </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -19065,7 +19081,7 @@
       <c r="V20" s="10"/>
       <c r="W20" s="10"/>
     </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -19076,7 +19092,7 @@
       <c r="V21" s="10"/>
       <c r="W21" s="10"/>
     </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -19087,7 +19103,7 @@
       <c r="V22" s="10"/>
       <c r="W22" s="10"/>
     </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -19098,11 +19114,11 @@
       <c r="V23" s="10"/>
       <c r="W23" s="10"/>
     </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:23" x14ac:dyDescent="0.35">
       <c r="E24" s="11"/>
       <c r="T24" s="10"/>
     </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:23" x14ac:dyDescent="0.35">
       <c r="E25" s="11"/>
     </row>
   </sheetData>
@@ -19124,19 +19140,19 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{244B4101-5D58-45D7-9A89-57EA3262A855}">
-  <dimension ref="A1:I24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:J24"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.453125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.26953125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -19165,7 +19181,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -19193,8 +19209,9 @@
       <c r="I2" s="10">
         <v>1.5001344999999999</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J2" s="10"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -19222,8 +19239,9 @@
       <c r="I3" s="10">
         <v>1.35022</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J3" s="10"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -19251,8 +19269,9 @@
       <c r="I4" s="10">
         <v>1.5768800000000001</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J4" s="10"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>38</v>
       </c>
@@ -19281,7 +19300,7 @@
         <v>1.1771042199999999</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>38</v>
       </c>
@@ -19310,7 +19329,7 @@
         <v>1.2602</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>38</v>
       </c>
@@ -19339,7 +19358,7 @@
         <v>1.8176399999999999</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>40</v>
       </c>
@@ -19368,7 +19387,7 @@
         <v>1.4087645999999998</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>40</v>
       </c>
@@ -19397,7 +19416,7 @@
         <v>1.55758</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>40</v>
       </c>
@@ -19426,16 +19445,16 @@
         <v>1.8697299999999999</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="E12" s="10"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
       <c r="D14" s="2"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -19445,7 +19464,7 @@
       <c r="G15" s="10"/>
       <c r="H15" s="10"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -19455,7 +19474,7 @@
       <c r="H16" s="10"/>
       <c r="I16" s="10"/>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -19465,7 +19484,7 @@
       <c r="H17" s="10"/>
       <c r="I17" s="10"/>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -19475,7 +19494,7 @@
       <c r="H18" s="10"/>
       <c r="I18" s="10"/>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -19485,7 +19504,7 @@
       <c r="H19" s="10"/>
       <c r="I19" s="10"/>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -19495,7 +19514,7 @@
       <c r="H20" s="10"/>
       <c r="I20" s="10"/>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -19505,7 +19524,7 @@
       <c r="H21" s="10"/>
       <c r="I21" s="10"/>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -19515,7 +19534,7 @@
       <c r="H22" s="10"/>
       <c r="I22" s="10"/>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -19525,7 +19544,7 @@
       <c r="H23" s="10"/>
       <c r="I23" s="10"/>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="F24" s="10"/>
     </row>
   </sheetData>
